--- a/artfynd/A 57773-2025 artfynd.xlsx
+++ b/artfynd/A 57773-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,39 +675,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104320347</v>
+        <v>104320346</v>
       </c>
       <c r="B2" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3624</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>737057.006083936</v>
+        <v>737129</v>
       </c>
       <c r="R2" t="n">
-        <v>6411048.199164519</v>
+        <v>6411014</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +739,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,39 +772,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104320348</v>
+        <v>104320365</v>
       </c>
       <c r="B3" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>737073.2373495585</v>
+        <v>737062</v>
       </c>
       <c r="R3" t="n">
-        <v>6411036.32753793</v>
+        <v>6411105</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +836,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +872,7 @@
         <v>104320364</v>
       </c>
       <c r="B4" t="n">
-        <v>85057</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>737024.7320586846</v>
+        <v>737024</v>
       </c>
       <c r="R4" t="n">
-        <v>6411077.833398191</v>
+        <v>6411078</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,19 +937,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104320351</v>
+        <v>104320348</v>
       </c>
       <c r="B5" t="n">
-        <v>87986</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245042</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>737073.2373495585</v>
+        <v>737073</v>
       </c>
       <c r="R5" t="n">
-        <v>6411036.32753793</v>
+        <v>6411037</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,19 +1038,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104320349</v>
+        <v>104320347</v>
       </c>
       <c r="B6" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,23 +1082,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>3624</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1179,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>737073.2373495585</v>
+        <v>737057</v>
       </c>
       <c r="R6" t="n">
-        <v>6411036.32753793</v>
+        <v>6411048</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,19 +1135,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,39 +1168,30 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104320365</v>
+        <v>104320363</v>
       </c>
       <c r="B7" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>433</v>
+        <v>3624</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1295,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>737062.2155268586</v>
+        <v>737062</v>
       </c>
       <c r="R7" t="n">
-        <v>6411105.166451611</v>
+        <v>6411105</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,19 +1232,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104320362</v>
+        <v>104320368</v>
       </c>
       <c r="B8" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,23 +1276,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3762</v>
+        <v>3624</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1411,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>737024.7320586846</v>
+        <v>736962</v>
       </c>
       <c r="R8" t="n">
-        <v>6411077.833398191</v>
+        <v>6410992</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1444,19 +1329,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104320363</v>
+        <v>104320372</v>
       </c>
       <c r="B9" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,14 +1382,10 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1527,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>737062.2155268586</v>
+        <v>737014</v>
       </c>
       <c r="R9" t="n">
-        <v>6411105.166451611</v>
+        <v>6410997</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1560,19 +1426,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,6 +1452,621 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104320349</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>737073</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6411037</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104320362</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>737024</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6411078</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105193458</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sundsnäset, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>737132</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6411001</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104320371</v>
+      </c>
+      <c r="B13" t="n">
+        <v>89870</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>737006</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6410985</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104320340</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90665</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>737129</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6411014</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104320351</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90665</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>737073</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6411037</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>

--- a/artfynd/A 57773-2025 artfynd.xlsx
+++ b/artfynd/A 57773-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320346</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320365</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320364</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320348</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320347</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320363</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320368</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320372</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320349</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320362</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1768,6 +1823,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105193458</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1869,6 +1929,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320371</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1970,6 +2035,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320340</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2071,8 +2141,29 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320351</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>